--- a/small_funds.xlsx
+++ b/small_funds.xlsx
@@ -1,441 +1,822 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learn\python\funds\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BA28BD-F665-46BF-8129-41375F351154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24750" windowHeight="10270"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="139">
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
   <si>
     <t>002834</t>
   </si>
   <si>
+    <t>华夏新锦绣</t>
+  </si>
+  <si>
     <t>003359</t>
   </si>
   <si>
+    <t>大成360</t>
+  </si>
+  <si>
     <t>004685</t>
   </si>
   <si>
+    <t>金元顺安元启</t>
+  </si>
+  <si>
     <t>005110</t>
   </si>
   <si>
+    <t>汇安多策略</t>
+  </si>
+  <si>
     <t>005141</t>
   </si>
   <si>
+    <t>华夏睿磐泰荣</t>
+  </si>
+  <si>
     <t>005178</t>
   </si>
   <si>
+    <t>华夏睿磐泰利</t>
+  </si>
+  <si>
     <t>006038</t>
   </si>
   <si>
+    <t>大成景恒</t>
+  </si>
+  <si>
     <t>007578</t>
   </si>
   <si>
+    <t>宝盈新锐</t>
+  </si>
+  <si>
     <t>011378</t>
   </si>
   <si>
+    <t>创金合信积极成长</t>
+  </si>
+  <si>
     <t>011730</t>
   </si>
   <si>
+    <t>工银聚享</t>
+  </si>
+  <si>
     <t>012877</t>
   </si>
   <si>
+    <t>富荣福耀</t>
+  </si>
+  <si>
     <t>014559</t>
   </si>
   <si>
+    <t>华商品质慧选</t>
+  </si>
+  <si>
     <t>014828</t>
   </si>
   <si>
+    <t>汇泉启元未来</t>
+  </si>
+  <si>
     <t>016913</t>
   </si>
   <si>
+    <t>恒越均衡优选</t>
+  </si>
+  <si>
     <t>017151</t>
   </si>
   <si>
+    <t>华夏泰兴</t>
+  </si>
+  <si>
     <t>017155</t>
   </si>
   <si>
+    <t>民生加银专精特新智选</t>
+  </si>
+  <si>
     <t>019339</t>
   </si>
   <si>
+    <t>创金合信启富</t>
+  </si>
+  <si>
     <t>020152</t>
   </si>
   <si>
+    <t>中信保诚景气优选</t>
+  </si>
+  <si>
     <t>020726</t>
   </si>
   <si>
+    <t>建信灵活配置</t>
+  </si>
+  <si>
     <t>519097</t>
   </si>
   <si>
+    <t>新华中小市值优选</t>
+  </si>
+  <si>
     <t>018561</t>
   </si>
   <si>
+    <t>中信保诚多策略</t>
+  </si>
+  <si>
     <t>320016</t>
   </si>
   <si>
-    <t>code</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>诺安多策略</t>
   </si>
   <si>
     <t>021364</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>渤海汇金新动能</t>
   </si>
   <si>
     <t>015881</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中欧小盘成长</t>
   </si>
   <si>
     <t>001414</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国联鑫起点</t>
   </si>
   <si>
     <t>005225</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>广发量化多因子</t>
   </si>
   <si>
     <t>015526</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大成动态量化</t>
   </si>
   <si>
     <t>020434</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金信量化精选</t>
   </si>
   <si>
     <t>014669</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>银华专精特新量化</t>
   </si>
   <si>
     <t>006195</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国金量化多因子</t>
   </si>
   <si>
     <t>014806</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国金量化精选</t>
   </si>
   <si>
     <t>021885</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>太平量化选股</t>
   </si>
   <si>
     <t>007950</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招商量化精选</t>
   </si>
   <si>
     <t>014996</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中欧量化先锋</t>
   </si>
   <si>
     <t>019723</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中银量化选股</t>
   </si>
   <si>
     <t>009841</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>东财量化精选</t>
   </si>
   <si>
     <t>020902</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>招商成长量化</t>
   </si>
   <si>
     <t>023387</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国泰聚智量化选股</t>
   </si>
   <si>
     <t>021991</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中加专精特新量化</t>
   </si>
   <si>
     <t>002496</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>华夏新锦绣</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>大成360</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金元顺安元启</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>汇安多策略</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>华夏睿磐泰荣</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>华夏睿磐泰利</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>大成景恒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝盈新锐</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>创金合信积极成长</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>工银聚享</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>富荣福耀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>华商品质慧选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>汇泉启元未来</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>恒越均衡优选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>华夏泰兴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>民生加银专精特新智选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>创金合信启富</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中信保诚景气优选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>建信灵活配置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新华中小市值优选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中信保诚多策略</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>诺安多策略</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>渤海汇金新动能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中欧小盘成长</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>国联鑫起点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>广发量化多因子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>大成动态量化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金信量化精选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>银华专精特新量化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>国金量化多因子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>国金量化精选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>太平量化选股</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>招商量化精选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中欧量化先锋</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中银量化选股</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>东财量化精选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>招商成长量化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>国泰聚智量化选股</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中加专精特新量化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>前海开源量化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>025448</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>万家元晟量化选股</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>006532</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>华泰柏瑞量化阿尔法</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>024500</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>兴华景和混合发起</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>001735</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>广发新锐智选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>020304</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>信澳星亮智选</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020305</t>
+  </si>
+  <si>
+    <t>信澳星煜智选</t>
   </si>
   <si>
     <t>025487</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>中邮新锐量化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>013034</t>
   </si>
   <si>
     <t>泰信智选量化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>013034</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>014003</t>
   </si>
   <si>
     <t>浦银安盛增长动力</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>014003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>005105</t>
   </si>
   <si>
     <t>富荣福康</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>005105</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>160323</t>
+  </si>
+  <si>
+    <t>华夏磐泰</t>
+  </si>
+  <si>
+    <t>003301</t>
+  </si>
+  <si>
+    <t>华夏鼎融</t>
+  </si>
+  <si>
+    <t>009730</t>
+  </si>
+  <si>
+    <t>中信保诚安鑫回报</t>
+  </si>
+  <si>
+    <t>015245</t>
+  </si>
+  <si>
+    <t>南华丰汇</t>
+  </si>
+  <si>
+    <t>021663</t>
+  </si>
+  <si>
+    <t>汇百川远航</t>
+  </si>
+  <si>
+    <t>022492</t>
+  </si>
+  <si>
+    <t>金元顺安鑫怡</t>
+  </si>
+  <si>
+    <t>005437</t>
+  </si>
+  <si>
+    <t>易方达易百智能量化</t>
+  </si>
+  <si>
+    <t>590001</t>
+  </si>
+  <si>
+    <t>中邮核心优选</t>
+  </si>
+  <si>
+    <t>001681</t>
+  </si>
+  <si>
+    <t>新华积极价值</t>
+  </si>
+  <si>
+    <t>001453</t>
+  </si>
+  <si>
+    <t>鹏华弘鑫</t>
+  </si>
+  <si>
+    <t>益民核心增长</t>
+  </si>
+  <si>
+    <t>020560</t>
+  </si>
+  <si>
+    <t>万家高端装备</t>
+  </si>
+  <si>
+    <t>001223</t>
+  </si>
+  <si>
+    <t>鹏华文化传媒娱乐</t>
+  </si>
+  <si>
+    <t>020491</t>
+  </si>
+  <si>
+    <t>万家医药量化</t>
+  </si>
+  <si>
+    <t>018730</t>
+  </si>
+  <si>
+    <t>华夏招鑫鸿瑞</t>
+  </si>
+  <si>
+    <t>015071</t>
+  </si>
+  <si>
+    <t>鑫元专精特精企业精选</t>
+  </si>
+  <si>
+    <t>001734</t>
+  </si>
+  <si>
+    <t>024499</t>
+  </si>
+  <si>
+    <t>兴发景和</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>018549</t>
+  </si>
+  <si>
+    <t>金鹰研究驱动</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -458,9 +839,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -472,17 +1095,61 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -767,348 +1434,348 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E73"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.63636363636364" customWidth="1"/>
+    <col min="2" max="2" width="22.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B22" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B26" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B27" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="29" spans="1:2">
+      <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="B29" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="30" spans="1:2">
+      <c r="A30" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="B30" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="31" spans="1:2">
+      <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="B31" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="32" spans="1:2">
+      <c r="A32" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="B32" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="33" spans="1:2">
+      <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="B33" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="34" spans="1:2">
+      <c r="A34" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="B34" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="35" spans="1:2">
+      <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="B35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="36" spans="1:2">
+      <c r="A36" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="B36" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="37" spans="1:2">
+      <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="B37" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="38" spans="1:2">
+      <c r="A38" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B38" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="39" spans="1:2">
+      <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="B39" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="40" spans="1:2">
+      <c r="A40" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="41" spans="1:2">
+      <c r="A41" s="3" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
         <v>82</v>
       </c>
@@ -1116,7 +1783,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -1124,7 +1791,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
         <v>86</v>
       </c>
@@ -1132,7 +1799,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -1140,7 +1807,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" s="3" t="s">
         <v>90</v>
       </c>
@@ -1148,7 +1815,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -1156,62 +1823,204 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
         <v>95</v>
       </c>
-      <c r="B48" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" t="s">
         <v>97</v>
       </c>
-      <c r="B49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" t="s">
         <v>99</v>
       </c>
-      <c r="B50" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="3"/>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>560006</v>
+      </c>
+      <c r="B62" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/small_funds.xlsx
+++ b/small_funds.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learn\python\funds\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DD52EB-64C2-4F45-9E3C-B661390693B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10270"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="136">
   <si>
     <t>code</t>
   </si>
@@ -429,15 +433,6 @@
   </si>
   <si>
     <t>001734</t>
-  </si>
-  <si>
-    <t>024499</t>
-  </si>
-  <si>
-    <t>兴发景和</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>018549</t>
@@ -449,14 +444,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,352 +460,21 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -839,251 +497,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1095,61 +511,17 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1434,20 +806,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B72"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.63636363636364" customWidth="1"/>
-    <col min="2" max="2" width="22.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="9.61328125" customWidth="1"/>
+    <col min="2" max="2" width="22.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1455,7 +827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1463,7 +835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1471,7 +843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1479,7 +851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1487,7 +859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1495,7 +867,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1503,7 +875,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1511,7 +883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1519,7 +891,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1527,7 +899,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1535,7 +907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1543,7 +915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1551,7 +923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1559,7 +931,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1567,7 +939,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1575,7 +947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1583,7 +955,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1591,7 +963,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1599,7 +971,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1607,7 +979,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1615,7 +987,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -1623,7 +995,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -1631,7 +1003,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
@@ -1639,7 +1011,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
@@ -1647,7 +1019,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -1655,7 +1027,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -1663,7 +1035,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
@@ -1671,7 +1043,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -1679,7 +1051,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>58</v>
       </c>
@@ -1687,7 +1059,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -1695,7 +1067,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>62</v>
       </c>
@@ -1703,7 +1075,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -1711,7 +1083,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>66</v>
       </c>
@@ -1719,7 +1091,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -1727,7 +1099,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>70</v>
       </c>
@@ -1735,7 +1107,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -1743,7 +1115,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>74</v>
       </c>
@@ -1751,7 +1123,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -1759,7 +1131,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>78</v>
       </c>
@@ -1767,7 +1139,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -1775,7 +1147,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>82</v>
       </c>
@@ -1783,7 +1155,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -1791,7 +1163,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>86</v>
       </c>
@@ -1799,7 +1171,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -1807,7 +1179,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>90</v>
       </c>
@@ -1815,7 +1187,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -1823,7 +1195,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>94</v>
       </c>
@@ -1831,7 +1203,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>96</v>
       </c>
@@ -1839,7 +1211,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>98</v>
       </c>
@@ -1847,7 +1219,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>100</v>
       </c>
@@ -1855,7 +1227,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>102</v>
       </c>
@@ -1863,7 +1235,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>104</v>
       </c>
@@ -1871,7 +1243,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>106</v>
       </c>
@@ -1879,7 +1251,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>108</v>
       </c>
@@ -1887,7 +1259,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>110</v>
       </c>
@@ -1895,7 +1267,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>112</v>
       </c>
@@ -1903,7 +1275,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>114</v>
       </c>
@@ -1911,7 +1283,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>116</v>
       </c>
@@ -1919,7 +1291,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>118</v>
       </c>
@@ -1927,7 +1299,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -1935,7 +1307,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>560006</v>
       </c>
@@ -1943,7 +1315,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>123</v>
       </c>
@@ -1951,7 +1323,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>125</v>
       </c>
@@ -1959,7 +1331,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>127</v>
       </c>
@@ -1967,7 +1339,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>129</v>
       </c>
@@ -1975,7 +1347,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>131</v>
       </c>
@@ -1983,7 +1355,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>133</v>
       </c>
@@ -1991,36 +1363,25 @@
         <v>89</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>134</v>
       </c>
       <c r="B69" t="s">
         <v>135</v>
       </c>
-      <c r="E69" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B70" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="3"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
     </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3"/>
-    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>